--- a/reports/2026-08_月次実績報告/excel/第51期8月実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期8月実績.xlsx
@@ -4682,7 +4682,9 @@
       <c r="K26" s="316" t="n">
         <v>38</v>
       </c>
-      <c r="L26" s="355" t="n"/>
+      <c r="L26" s="355" t="n">
+        <v>286.455</v>
+      </c>
       <c r="M26" s="359">
         <f>L26-K26</f>
         <v/>
@@ -4704,7 +4706,9 @@
       <c r="R26" s="316" t="n">
         <v>0.25</v>
       </c>
-      <c r="S26" s="355" t="n"/>
+      <c r="S26" s="355" t="n">
+        <v>25.625</v>
+      </c>
       <c r="T26" s="359">
         <f>S26-R26</f>
         <v/>

--- a/reports/2026-08_月次実績報告/excel/第51期8月実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期8月実績.xlsx
@@ -4682,9 +4682,7 @@
       <c r="K26" s="316" t="n">
         <v>38</v>
       </c>
-      <c r="L26" s="355" t="n">
-        <v>286.455</v>
-      </c>
+      <c r="L26" s="355" t="n"/>
       <c r="M26" s="359">
         <f>L26-K26</f>
         <v/>
@@ -4706,9 +4704,7 @@
       <c r="R26" s="316" t="n">
         <v>0.25</v>
       </c>
-      <c r="S26" s="355" t="n">
-        <v>25.625</v>
-      </c>
+      <c r="S26" s="355" t="n"/>
       <c r="T26" s="359">
         <f>S26-R26</f>
         <v/>

--- a/reports/2026-08_月次実績報告/excel/第51期8月実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期8月実績.xlsx
@@ -3837,7 +3837,7 @@
         <v>8030</v>
       </c>
       <c r="S16" s="306" t="n">
-        <v>9530.098</v>
+        <v>9525.098</v>
       </c>
       <c r="T16" s="308">
         <f>S16-R16</f>
@@ -4273,7 +4273,7 @@
         <v>6810</v>
       </c>
       <c r="S21" s="357" t="n">
-        <v>9152.914500000001</v>
+        <v>9150.3045</v>
       </c>
       <c r="T21" s="308">
         <f>S21-R21</f>
